--- a/QCM1_4_PHY.xlsx
+++ b/QCM1_4_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFD31BE-4F3C-452F-812B-43F800DC0A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E79B8DF-201E-44F9-8B29-119B17012849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="188">
   <si>
     <t>Question</t>
   </si>
@@ -102,9 +102,6 @@
     <t>La dispersion par un prisme est l'équivalent de la diffraction pour les ondes mécaniques progressives.</t>
   </si>
   <si>
-    <t>Un prisme : On considère un prisme, d'arrête A, constitué d'un verre d'indice n pour une radiation jaune. On fait arriver une radiation jaune sur la face d'entrée du prisme sous une incidence i. Les radiations jaunes seront moins déviées que...</t>
-  </si>
-  <si>
     <t>inversement proportionnelle à l'indice n</t>
   </si>
   <si>
@@ -138,9 +135,6 @@
     <t>$\lambda = 8000\text{ nm}$</t>
   </si>
   <si>
-    <t>Un laser à $CO_2$ : On utilise un laser à $CO_2$ produisant une lumière de longueur d'onde $\lambda$ comprise entre $9\text{ \mu m}$ et $11,5\text{ \mu m}$ placé devant une fente de largeur $a$ et d'un écran.</t>
-  </si>
-  <si>
     <t>$600\text{ nm} &lt; \lambda &lt; 800\text{ nm}$</t>
   </si>
   <si>
@@ -165,9 +159,6 @@
     <t>au domaine des rayons X</t>
   </si>
   <si>
-    <t>On observe la figure suivante, constituée de tâches lumineuses, sur l'écran placé à une distance D de la fente.</t>
-  </si>
-  <si>
     <t>de dispersion</t>
   </si>
   <si>
@@ -180,9 +171,6 @@
     <t>de réflexion</t>
   </si>
   <si>
-    <t>Phénomène de diffraction : un rayon laser de longueur d'onde dans le vide $\lambda = 600\text{ nm}$ traverse une fente verticale de largeur a. On place un écran à une distance D. Célérité $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
-  </si>
-  <si>
     <t>Rouge</t>
   </si>
   <si>
@@ -231,9 +219,6 @@
     <t>$L = \frac{\lambda D}{2a}$</t>
   </si>
   <si>
-    <t>Un faisceau lumineux monochromatique : On éclaire un fil très fin vertical, de diamètre a, avec un faisceau lumineux monochromatique de fréquence $\nu = 5 \cdot 10^{14}\text{ Hz}$. On observe le phénomène de diffraction sur un écran situé à une distance $D = 3\text{ m}$ du fil. La largeur de la tache centrale est $L = 30\text{ mm}$.</t>
-  </si>
-  <si>
     <t>La lumière est une onde transversale qui a la même vitesse dans tous les milieux transparents.</t>
   </si>
   <si>
@@ -264,9 +249,6 @@
     <t>$a = 1,2\text{ \mu m}$</t>
   </si>
   <si>
-    <t>Diffraction : On réalise l'expérience suivante, à l'aide d'un laser émettant une lumière monochromatique de longueur d'onde $\lambda$. A quelques centimètres du laser, on place successivement des fils verticaux de diamètres connus. On désigne par a le diamètre du fil. La figure obtenue est observée sur un écran blanc situé à une distance $D = 1,80\text{ m}$ des fils. Pour chacun des fils, on mesure la largeur L de la tache centrale. A partir de ces mesures et des données, il est possible de calculer la grandeur $1/a$. On donne: $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
-  </si>
-  <si>
     <t>réflexion</t>
   </si>
   <si>
@@ -300,9 +282,6 @@
     <t>$3,375 \cdot 10^{10}\text{ Hz}$</t>
   </si>
   <si>
-    <t>Une radiation lumineuse : Une radiation lumineuse visible de fréquence $\nu = 5 \cdot 10^{14}\text{ Hz}$ a une longueur d'onde $\lambda = 400\text{ nm}$ dans un milieu transparent d'indice n. Donnée : vitesse de propagation de la lumière dans le vide : $c = 3 \cdot 10^8\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
     <t>$\lambda_0 = 760\text{ nm}$</t>
   </si>
   <si>
@@ -333,9 +312,6 @@
     <t>$n = 1,0$</t>
   </si>
   <si>
-    <t>Diffraction : On éclaire un fil très fin de diamètre a par un laser qui émet une radiation de longueur d'onde $\lambda_1 = 670\text{ nm}$. On observe une figure de diffraction sur l'écran situé à la distance $D = 1,5\text{ m}$ du fil la largeur de la tache centrale $L_1 = 2\text{ cm}$. On remplace le laser par un autre qui émet une radiation de longueur d'onde $\lambda_2 = 560\text{ nm}$. La largeur de la tache centrale dans ce cas est notée $L_2$. Donnée : $56/67 = 0,84$</t>
-  </si>
-  <si>
     <t>$L_2 = 1,5\text{ cm}$</t>
   </si>
   <si>
@@ -366,9 +342,6 @@
     <t>$\theta = 2,4 \cdot 10^{-2}\text{ rad}$</t>
   </si>
   <si>
-    <t>Une lumière monochromatique : On éclaire une fente de largeur a par une lumière monochromatique de fréquence N émise par un laser. La figure de diffraction est observée sur un écran placé à une distance D de la fente. La largeur de la tache centrale est notée L. Avec un laser émettant une lumière verte de fréquence $N_v = 5,36 \cdot 10^{14}\text{ Hz}$, on obtient une tache centrale de largeur $L_v = 8,6\text{ mm}$. Avec un laser émettant une lumière rouge de fréquence $N_r = 4,74 \cdot 10^{14}\text{ Hz}$, on obtient une tache centrale de largeur $L_r$. Données : $\tan(\theta) \approx \theta(\text{rad})$ ; $268/237 = 1,13$</t>
-  </si>
-  <si>
     <t>$L_r = 10\text{ mm}$</t>
   </si>
   <si>
@@ -384,9 +357,6 @@
     <t>$L_r = 6,8\text{ mm}$</t>
   </si>
   <si>
-    <t>Indice de réfraction d'un milieu transparent : On réalise la diffraction d'une lumière monochromatique dans l'air et dans un milieu transparent d'indice n en utilisant le dispositif schématisé sur la figure 2. Le dispositif comporte un laser, un fil fin de diamètre a et un écran placé à la distance D du fil. On désigne par $\theta$ l'écart angulaire de diffraction. Donnée: pour $\theta$ très petit $\tan \theta \approx \theta(\text{rad})$</t>
-  </si>
-  <si>
     <t>Dans le vide sa longueur d'onde comprise entre $4\text{ \mu m}$ et $8\text{ \mu m}$.</t>
   </si>
   <si>
@@ -399,9 +369,6 @@
     <t>Constitué d'une seule radiation lumineuse d'une fréquence correspondant à une couleur.</t>
   </si>
   <si>
-    <t>Le dispositif est placé dans l'air, le laser émet une radiation monochromatique de longueur d'onde $\lambda_0$.</t>
-  </si>
-  <si>
     <t>$\lambda_0 = \frac{2D}{L_0 a}$</t>
   </si>
   <si>
@@ -417,9 +384,6 @@
     <t>$\lambda_0 = \frac{L_0 a}{D}$</t>
   </si>
   <si>
-    <t>On refait la même expérience en plaçant le fil et l'écran dans le milieu transparent d'indice n en gardant la même distance D. la largeur de la tache centrale observée sur l'écran est $L = 1,4\text{ cm}$.</t>
-  </si>
-  <si>
     <t>$n = L_0 \cdot L$</t>
   </si>
   <si>
@@ -450,9 +414,6 @@
     <t>$n = 1,56$</t>
   </si>
   <si>
-    <t>La longueur d'onde : On réalise la diffraction de la lumière en utilisant un laser qui donne une lumière monochromatique de longueur d'onde $\lambda$ dans l'air. Cette lumière traverse une fente de largeur a réglable. On obtient une figure de diffraction sur un écran situé à une distance de la fente. On mesure l'écart angulaire $\theta$ pour différentes valeurs de largeur de la fente. La courbe ci-contre représente les variations de $\theta$ en fonction de $1/a$.</t>
-  </si>
-  <si>
     <t>$\lambda = 400\text{ nm}$</t>
   </si>
   <si>
@@ -531,9 +492,6 @@
     <t>Les radiations du laser utilisé appartiennent :</t>
   </si>
   <si>
-    <t>On observe un phénomène :</t>
-  </si>
-  <si>
     <t>Le faisceau est de couleur :</t>
   </si>
   <si>
@@ -585,12 +543,6 @@
     <t>La lumière monochromatique est :</t>
   </si>
   <si>
-    <t>La largeur de la tache centrale observée sur l'écran est $L_0 = 1,9\text{ cm}$. L'expression de $\lambda_0$ est :</t>
-  </si>
-  <si>
-    <t>L'expression de l'indice n en fonction de $L_0$ et L vaut :</t>
-  </si>
-  <si>
     <t>La valeur de n est :</t>
   </si>
   <si>
@@ -598,6 +550,58 @@
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Ondes lumineuses :&lt;/b&gt;&lt;/center&gt;</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un prisme : &lt;/b&gt;&lt;/center&gt;
+On considère un prisme, d'arrête A, constitué d'un verre d'indice n pour une radiation jaune. On fait arriver une radiation jaune sur la face d'entrée du prisme sous une incidence i. Les radiations jaunes seront moins déviées que...</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un laser à $CO_2$ : &lt;/b&gt;&lt;/center&gt;
+On utilise un laser à $CO_2$ produisant une lumière de longueur d'onde $\lambda$ comprise entre $9 \, \mu \text{m}$ et $11,5 \, \mu \text{m}$ placé devant une fente de largeur $a$ et d'un écran.</t>
+  </si>
+  <si>
+    <t>On observe la figure suivante, constituée de tâches lumineuses, sur l'écran placé à une distance D de la fente.
+On observe un phénomène :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Phénomène de diffraction : &lt;/b&gt;&lt;/center&gt;
+un rayon laser de longueur d'onde dans le vide $\lambda = 600\text{ nm}$ traverse une fente verticale de largeur a. On place un écran à une distance D. Célérité $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un faisceau lumineux monochromatique : &lt;/b&gt;&lt;/center&gt;
+On éclaire un fil très fin vertical, de diamètre a, avec un faisceau lumineux monochromatique de fréquence $\nu = 5 \cdot 10^{14}\text{ Hz}$. On observe le phénomène de diffraction sur un écran situé à une distance $D = 3\text{ m}$ du fil. La largeur de la tache centrale est $L = 30\text{ mm}$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Diffraction : &lt;/b&gt;&lt;/center&gt;
+On réalise l'expérience suivante, à l'aide d'un laser émettant une lumière monochromatique de longueur d'onde $\lambda$. A quelques centimètres du laser, on place successivement des fils verticaux de diamètres connus. On désigne par a le diamètre du fil. La figure obtenue est observée sur un écran blanc situé à une distance $D = 1,80\text{ m}$ des fils. Pour chacun des fils, on mesure la largeur L de la tache centrale. A partir de ces mesures et des données, il est possible de calculer la grandeur $1/a$. On donne: $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Une radiation lumineuse : &lt;/b&gt;&lt;/center&gt;
+Une radiation lumineuse visible de fréquence $\nu = 5 \cdot 10^{14}\text{ Hz}$ a une longueur d'onde $\lambda = 400\text{ nm}$ dans un milieu transparent d'indice n. Donnée : vitesse de propagation de la lumière dans le vide : $c = 3 \cdot 10^8\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Diffraction : &lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On éclaire un fil très fin de diamètre a par un laser qui émet une radiation de longueur d'onde $\lambda_1 = 670\text{ nm}$. On observe une figure de diffraction sur l'écran situé à la distance $D = 1,5\text{ m}$ du fil la largeur de la tache centrale $L_1 = 2\text{ cm}$. On remplace le laser par un autre qui émet une radiation de longueur d'onde $\lambda_2 = 560\text{ nm}$. La largeur de la tache centrale dans ce cas est notée $L_2$. Donnée : $56/67 = 0,84$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Une lumière monochromatique : &lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On éclaire une fente de largeur a par une lumière monochromatique de fréquence N émise par un laser. La figure de diffraction est observée sur un écran placé à une distance D de la fente. La largeur de la tache centrale est notée L. Avec un laser émettant une lumière verte de fréquence $N_v = 5,36 \cdot 10^{14}\text{ Hz}$, on obtient une tache centrale de largeur $L_v = 8,6\text{ mm}$. Avec un laser émettant une lumière rouge de fréquence $N_r = 4,74 \cdot 10^{14}\text{ Hz}$, on obtient une tache centrale de largeur $L_r$. Données : $\tan(\theta) \approx \theta(\text{rad})$ ; $268/237 = 1,13$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Indice de réfraction d'un milieu transparent : &lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On réalise la diffraction d'une lumière monochromatique dans l'air et dans un milieu transparent d'indice n en utilisant le dispositif schématisé sur la figure 2. Le dispositif comporte un laser, un fil fin de diamètre a et un écran placé à la distance D du fil. On désigne par $\theta$ l'écart angulaire de diffraction. Donnée: pour $\theta$ très petit $\tan \theta \approx \theta(\text{rad})$</t>
+  </si>
+  <si>
+    <t>Le dispositif est placé dans l'air, le laser émet une radiation monochromatique de longueur d'onde $\lambda_0$.
+&lt;br&gt;La largeur de la tache centrale observée sur l'écran est $L_0 = 1,9\text{ cm}$. L'expression de $\lambda_0$ est :</t>
+  </si>
+  <si>
+    <t>On refait la même expérience en plaçant le fil et l'écran dans le milieu transparent d'indice n en gardant la même distance D. la largeur de la tache centrale observée sur l'écran est $L = 1,4\text{ cm}$.
+&lt;br&gt;L'expression de l'indice n en fonction de $L_0$ et L vaut :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La longueur d'onde : &lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;On réalise la diffraction de la lumière en utilisant un laser qui donne une lumière monochromatique de longueur d'onde $\lambda$ dans l'air. Cette lumière traverse une fente de largeur a réglable. On obtient une figure de diffraction sur un écran situé à une distance de la fente. On mesure l'écart angulaire $\theta$ pour différentes valeurs de largeur de la fente. La courbe ci-contre représente les variations de $\theta$ en fonction de $1/a$.</t>
   </si>
 </sst>
 </file>
@@ -1125,10 +1129,10 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>3</v>
@@ -1156,30 +1160,33 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>134</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="F3" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="G3" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="I3" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="5"/>
@@ -1187,26 +1194,26 @@
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="5"/>
@@ -1214,28 +1221,28 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="7" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>14</v>
@@ -1245,61 +1252,61 @@
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="7" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>16</v>
@@ -1309,90 +1316,88 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="7" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:11" ht="51" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>56</v>
-      </c>
       <c r="I10" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1400,28 +1405,28 @@
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="7" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1429,28 +1434,28 @@
     <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="7" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1458,28 +1463,28 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="7" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>17</v>
@@ -1489,61 +1494,61 @@
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="7" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>73</v>
-      </c>
       <c r="I15" s="9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -1551,59 +1556,59 @@
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -1611,370 +1616,366 @@
     <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="7" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="7" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="7" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="7" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I26" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" s="9" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>135</v>
-      </c>
       <c r="I28" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="7" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/QCM1_4_PHY.xlsx
+++ b/QCM1_4_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E79B8DF-201E-44F9-8B29-119B17012849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C489331-2CFF-4C69-8870-FFA91E62B107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="187">
   <si>
     <t>Question</t>
   </si>
@@ -66,27 +66,6 @@
     <t>Autre réponse</t>
   </si>
   <si>
-    <t>PHY_QCM1_1_Q12.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_1_Q13.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_1_Q14.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_1_Q15.png; PHY_QCM1_1_Q16.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_1_Q17.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_1_Q18.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_1_Q19.png</t>
-  </si>
-  <si>
     <t>La lumière est une onde transversale dont la célérité est la même dans tous les milieux transparents</t>
   </si>
   <si>
@@ -138,15 +117,6 @@
     <t>$600\text{ nm} &lt; \lambda &lt; 800\text{ nm}$</t>
   </si>
   <si>
-    <t>$400\text{ \mu m} &lt; \lambda &lt; 800\text{ \mu m}$</t>
-  </si>
-  <si>
-    <t>$0,4\text{ \mu m} &lt; \lambda &lt; 0,8\text{ \mu m}$</t>
-  </si>
-  <si>
-    <t>$40\text{ \mu m} &lt; \lambda &lt; 80\text{ \mu m}$</t>
-  </si>
-  <si>
     <t>au domaine des U.V.</t>
   </si>
   <si>
@@ -240,15 +210,6 @@
     <t>$a = 6 \cdot 10^{-5}\text{ m}$</t>
   </si>
   <si>
-    <t>$a = 6\text{ \mu m}$</t>
-  </si>
-  <si>
-    <t>$a = 5\text{ \mu m}$</t>
-  </si>
-  <si>
-    <t>$a = 1,2\text{ \mu m}$</t>
-  </si>
-  <si>
     <t>réflexion</t>
   </si>
   <si>
@@ -357,9 +318,6 @@
     <t>$L_r = 6,8\text{ mm}$</t>
   </si>
   <si>
-    <t>Dans le vide sa longueur d'onde comprise entre $4\text{ \mu m}$ et $8\text{ \mu m}$.</t>
-  </si>
-  <si>
     <t>Dans le vide sa longueur d'onde comprise entre $4 \cdot 10^4\text{ pm}$ et $8 \cdot 10^4\text{ pm}$.</t>
   </si>
   <si>
@@ -457,21 +415,6 @@
   </si>
   <si>
     <t>$3,375 \cdot 10^{14}\text{ Hz}$</t>
-  </si>
-  <si>
-    <t>$\teta_{r} = 1,13 \teta_{v}$</t>
-  </si>
-  <si>
-    <t>$\teta_{r} = 0,88 \teta_{v}$</t>
-  </si>
-  <si>
-    <t>$\teta_{r} = 11,3 \teta_{v}$</t>
-  </si>
-  <si>
-    <t>$\teta_{r} = 1,90 \teta_{v}$</t>
-  </si>
-  <si>
-    <t>$\teta_{r} = 2,26 \teta_{v}$</t>
   </si>
   <si>
     <t>Choisir la réponse juste :</t>
@@ -602,6 +545,60 @@
   <si>
     <t>&lt;center&gt;&lt;b&gt;La longueur d'onde : &lt;/b&gt;&lt;/center&gt;
 &lt;br&gt;On réalise la diffraction de la lumière en utilisant un laser qui donne une lumière monochromatique de longueur d'onde $\lambda$ dans l'air. Cette lumière traverse une fente de largeur a réglable. On obtient une figure de diffraction sur un écran situé à une distance de la fente. On mesure l'écart angulaire $\theta$ pour différentes valeurs de largeur de la fente. La courbe ci-contre représente les variations de $\theta$ en fonction de $1/a$.</t>
+  </si>
+  <si>
+    <t>PHY_QCM4_1_Q1.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM4_1_Q2.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM4_1_Q3.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM4_1_Q4.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM4_1_Q5.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM4_1_Q6.png</t>
+  </si>
+  <si>
+    <t>$400 \, \mu \text{m} &lt; \lambda &lt; 800 \, \mu \text{m}$</t>
+  </si>
+  <si>
+    <t>$0,4 \, \mu \text{m} &lt; \lambda &lt; 0,8 \, \mu \text{m}$</t>
+  </si>
+  <si>
+    <t>$40 \, \mu \text{m} &lt; \lambda &lt; 80 \, \mu \text{m}$</t>
+  </si>
+  <si>
+    <t>$a = 6 \, \mu \text{m}$</t>
+  </si>
+  <si>
+    <t>$a = 5 \, \mu \text{m}$</t>
+  </si>
+  <si>
+    <t>$a = 1,2 \, \mu \text{m}$</t>
+  </si>
+  <si>
+    <t>$\theta_{r} = 1,13 \theta_{v}$</t>
+  </si>
+  <si>
+    <t>$\theta_{r} = 0,88 \theta_{v}$</t>
+  </si>
+  <si>
+    <t>$\theta_{r} = 11,3 \theta_{v}$</t>
+  </si>
+  <si>
+    <t>$\theta_{r} = 1,90 \theta_{v}$</t>
+  </si>
+  <si>
+    <t>$\theta_{r} = 2,26 \theta_{v}$</t>
+  </si>
+  <si>
+    <t>Dans le vide sa longueur d'onde comprise entre $4 \, \mu \text{m}$ et $8 \, \mu \text{m}$.</t>
   </si>
 </sst>
 </file>
@@ -1129,64 +1126,62 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>13</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J2" s="4"/>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="5"/>
@@ -1194,26 +1189,26 @@
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="5"/>
@@ -1221,123 +1216,117 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="7" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>14</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="J5" s="4"/>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="7" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>15</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J6" s="6"/>
       <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="G7" s="9" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="7" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="5"/>
@@ -1345,88 +1334,92 @@
     <row r="9" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="9" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>169</v>
+      </c>
       <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="5"/>
+        <v>38</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>170</v>
+      </c>
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="7" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1434,28 +1427,28 @@
     <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1463,92 +1456,88 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="7" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>17</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J13" s="5"/>
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="7" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="J14" s="5"/>
       <c r="K14" s="5"/>
     </row>
     <row r="15" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -1556,59 +1545,59 @@
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -1616,366 +1605,375 @@
     <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="7" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="7" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>96</v>
+        <v>83</v>
+      </c>
+      <c r="J22" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="7" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>106</v>
+        <v>93</v>
+      </c>
+      <c r="J24" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="7" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="J25" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>113</v>
+        <v>99</v>
+      </c>
+      <c r="J26" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="9" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="7" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>130</v>
+        <v>116</v>
+      </c>
+      <c r="J30" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/QCM1_4_PHY.xlsx
+++ b/QCM1_4_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C489331-2CFF-4C69-8870-FFA91E62B107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBDADF2-A7A4-447A-8EB9-27A8617FEA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
